--- a/Team-Data/2012-13/2-9-2012-13.xlsx
+++ b/Team-Data/2012-13/2-9-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
@@ -784,7 +851,7 @@
         <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -814,7 +881,7 @@
         <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -993,10 +1060,10 @@
         <v>14</v>
       </c>
       <c r="BB3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>0.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>11</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1133,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" t="n">
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.22</v>
+        <v>0.224</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="J5" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.423</v>
+        <v>0.425</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
@@ -1237,22 +1304,22 @@
         <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.346</v>
+        <v>0.35</v>
       </c>
       <c r="O5" t="n">
         <v>19.4</v>
       </c>
       <c r="P5" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.754</v>
+        <v>0.752</v>
       </c>
       <c r="R5" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S5" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T5" t="n">
         <v>40.8</v>
@@ -1261,31 +1328,31 @@
         <v>18.9</v>
       </c>
       <c r="V5" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X5" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.09999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="AC5" t="n">
         <v>-8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1303,19 +1370,19 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM5" t="n">
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1324,7 +1391,7 @@
         <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>15</v>
@@ -1339,7 +1406,7 @@
         <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
@@ -1497,10 +1564,10 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1512,13 +1579,13 @@
         <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>0.314</v>
+        <v>0.32</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1601,34 +1668,34 @@
         <v>20.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O7" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P7" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R7" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S7" t="n">
         <v>28.6</v>
       </c>
       <c r="T7" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U7" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V7" t="n">
         <v>14.3</v>
       </c>
       <c r="W7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X7" t="n">
         <v>3.7</v>
@@ -1643,19 +1710,19 @@
         <v>20.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.3</v>
+        <v>-4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
         <v>27</v>
@@ -1664,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -1685,7 +1752,7 @@
         <v>12</v>
       </c>
       <c r="AP7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
@@ -1697,13 +1764,13 @@
         <v>29</v>
       </c>
       <c r="AT7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW7" t="n">
         <v>12</v>
@@ -1715,13 +1782,13 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA7" t="n">
         <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
         <v>26</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
         <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.44</v>
+        <v>0.429</v>
       </c>
       <c r="H8" t="n">
         <v>49</v>
@@ -1771,67 +1838,67 @@
         <v>38.2</v>
       </c>
       <c r="J8" t="n">
-        <v>84.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L8" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
         <v>19.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.366</v>
+        <v>0.362</v>
       </c>
       <c r="O8" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="R8" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S8" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U8" t="n">
         <v>22.6</v>
       </c>
       <c r="V8" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W8" t="n">
         <v>7.8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>100.9</v>
+        <v>100.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.8</v>
+        <v>-2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1858,13 +1925,13 @@
         <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
         <v>17</v>
@@ -1876,7 +1943,7 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
@@ -1885,7 +1952,7 @@
         <v>11</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW8" t="n">
         <v>16</v>
@@ -1903,10 +1970,10 @@
         <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.647</v>
+        <v>0.64</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,7 +2020,7 @@
         <v>40.1</v>
       </c>
       <c r="J9" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="K9" t="n">
         <v>0.471</v>
@@ -1968,13 +2035,13 @@
         <v>0.338</v>
       </c>
       <c r="O9" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="P9" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>13.6</v>
@@ -1989,7 +2056,7 @@
         <v>23.9</v>
       </c>
       <c r="V9" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W9" t="n">
         <v>8.6</v>
@@ -2007,16 +2074,16 @@
         <v>22.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>104.8</v>
+        <v>104.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE9" t="n">
         <v>5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>4</v>
       </c>
       <c r="AF9" t="n">
         <v>6</v>
@@ -2025,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2037,7 +2104,7 @@
         <v>4</v>
       </c>
       <c r="AL9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM9" t="n">
         <v>17</v>
@@ -2067,7 +2134,7 @@
         <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.385</v>
+        <v>0.373</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
@@ -2138,7 +2205,7 @@
         <v>81.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L10" t="n">
         <v>6.1</v>
@@ -2147,7 +2214,7 @@
         <v>16.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.365</v>
+        <v>0.362</v>
       </c>
       <c r="O10" t="n">
         <v>16.2</v>
@@ -2156,28 +2223,28 @@
         <v>23.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.697</v>
+        <v>0.696</v>
       </c>
       <c r="R10" t="n">
         <v>12.8</v>
       </c>
       <c r="S10" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T10" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U10" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y10" t="n">
         <v>5.5</v>
@@ -2186,16 +2253,16 @@
         <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>95.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2204,28 +2271,28 @@
         <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AM10" t="n">
         <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO10" t="n">
         <v>21</v>
@@ -2240,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>5</v>
@@ -2249,7 +2316,7 @@
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>28</v>
@@ -2267,7 +2334,7 @@
         <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -2299,103 +2366,103 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
         <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.588</v>
+        <v>0.6</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J11" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.456</v>
+        <v>0.458</v>
       </c>
       <c r="L11" t="n">
         <v>7.8</v>
       </c>
       <c r="M11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.392</v>
+        <v>0.393</v>
       </c>
       <c r="O11" t="n">
         <v>17</v>
       </c>
       <c r="P11" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.799</v>
+        <v>0.801</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S11" t="n">
         <v>33.6</v>
       </c>
       <c r="T11" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="U11" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="V11" t="n">
         <v>15.2</v>
       </c>
       <c r="W11" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y11" t="n">
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.9</v>
+        <v>101.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI11" t="n">
         <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
         <v>9</v>
@@ -2410,16 +2477,16 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2428,7 +2495,7 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
         <v>25</v>
@@ -2449,10 +2516,10 @@
         <v>23</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -2565,10 +2632,10 @@
         <v>12</v>
       </c>
       <c r="AF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG12" t="n">
         <v>14</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -2610,13 +2677,13 @@
         <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
         <v>27</v>
@@ -2628,7 +2695,7 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
         <v>2</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2771,7 +2838,7 @@
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO13" t="n">
         <v>17</v>
@@ -2792,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -2953,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
         <v>16</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
         <v>4</v>
@@ -3147,7 +3214,7 @@
         <v>29</v>
       </c>
       <c r="AR15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS15" t="n">
         <v>3</v>
@@ -3156,7 +3223,7 @@
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>7</v>
@@ -3305,7 +3372,7 @@
         <v>23</v>
       </c>
       <c r="AJ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK16" t="n">
         <v>25</v>
@@ -3347,7 +3414,7 @@
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>22</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3526,7 +3593,7 @@
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX17" t="n">
         <v>18</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -3573,46 +3640,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" t="n">
         <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
-        <v>0.51</v>
+        <v>0.521</v>
       </c>
       <c r="H18" t="n">
         <v>48.2</v>
       </c>
       <c r="I18" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J18" t="n">
         <v>86.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
         <v>18.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O18" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="P18" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.738</v>
+        <v>0.734</v>
       </c>
       <c r="R18" t="n">
         <v>13</v>
@@ -3621,16 +3688,16 @@
         <v>30.5</v>
       </c>
       <c r="T18" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="U18" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V18" t="n">
         <v>14.6</v>
       </c>
       <c r="W18" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X18" t="n">
         <v>7.5</v>
@@ -3639,25 +3706,25 @@
         <v>4.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA18" t="n">
         <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
@@ -3681,7 +3748,7 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
@@ -3699,16 +3766,16 @@
         <v>16</v>
       </c>
       <c r="AT18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV18" t="n">
         <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>1</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3909,7 @@
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
         <v>27</v>
@@ -3851,7 +3918,7 @@
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3881,7 +3948,7 @@
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
         <v>19</v>
@@ -3908,7 +3975,7 @@
         <v>21</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>-4</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF20" t="n">
         <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH20" t="n">
         <v>16</v>
@@ -4036,7 +4103,7 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>15</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>5.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF21" t="n">
         <v>4</v>
@@ -4218,7 +4285,7 @@
         <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4236,10 +4303,10 @@
         <v>23</v>
       </c>
       <c r="AQ21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR21" t="n">
         <v>18</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>21</v>
@@ -4269,7 +4336,7 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC21" t="n">
         <v>5</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI22" t="n">
         <v>4</v>
@@ -4424,7 +4491,7 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -4448,7 +4515,7 @@
         <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4579,10 +4646,10 @@
         <v>10</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL23" t="n">
         <v>17</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -4665,67 +4732,67 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
         <v>27</v>
       </c>
       <c r="G24" t="n">
-        <v>0.449</v>
+        <v>0.438</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J24" t="n">
-        <v>84.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L24" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M24" t="n">
         <v>17.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.348</v>
+        <v>0.352</v>
       </c>
       <c r="O24" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="P24" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="Q24" t="n">
         <v>0.718</v>
       </c>
       <c r="R24" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="S24" t="n">
-        <v>30.9</v>
+        <v>30.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.6</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
         <v>22.3</v>
       </c>
       <c r="V24" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="X24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y24" t="n">
         <v>4.5</v>
@@ -4737,13 +4804,13 @@
         <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>-2.8</v>
+        <v>-3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
@@ -4767,13 +4834,13 @@
         <v>18</v>
       </c>
       <c r="AL24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,10 +4855,10 @@
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>14</v>
@@ -4803,7 +4870,7 @@
         <v>21</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY24" t="n">
         <v>7</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>-4.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF25" t="n">
         <v>26</v>
@@ -4949,10 +5016,10 @@
         <v>17</v>
       </c>
       <c r="AL25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN25" t="n">
         <v>29</v>
@@ -4964,7 +5031,7 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
         <v>17</v>
@@ -4997,7 +5064,7 @@
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5143,7 +5210,7 @@
         <v>20</v>
       </c>
       <c r="AP26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ26" t="n">
         <v>9</v>
@@ -5161,7 +5228,7 @@
         <v>22</v>
       </c>
       <c r="AV26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW26" t="n">
         <v>24</v>
@@ -5179,10 +5246,10 @@
         <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -5211,88 +5278,88 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27" t="n">
         <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>0.353</v>
+        <v>0.34</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J27" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L27" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M27" t="n">
         <v>18.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P27" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.75</v>
+        <v>0.752</v>
       </c>
       <c r="R27" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S27" t="n">
         <v>28.3</v>
       </c>
       <c r="T27" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U27" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V27" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
         <v>4.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
         <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.3</v>
+        <v>95.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.9</v>
+        <v>-7.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
@@ -5301,37 +5368,37 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK27" t="n">
         <v>23</v>
       </c>
       <c r="AL27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM27" t="n">
         <v>21</v>
       </c>
       <c r="AN27" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR27" t="n">
         <v>12</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>11</v>
       </c>
       <c r="AS27" t="n">
         <v>30</v>
@@ -5346,7 +5413,7 @@
         <v>19</v>
       </c>
       <c r="AW27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
         <v>24</v>
@@ -5358,10 +5425,10 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5519,7 +5586,7 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
@@ -5665,10 +5732,10 @@
         <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ29" t="n">
         <v>14</v>
@@ -5683,7 +5750,7 @@
         <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO29" t="n">
         <v>13</v>
@@ -5695,7 +5762,7 @@
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
         <v>28</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E30" t="n">
         <v>28</v>
       </c>
       <c r="F30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.538</v>
+        <v>0.549</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J30" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K30" t="n">
         <v>0.451</v>
@@ -5787,16 +5854,16 @@
         <v>16.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O30" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P30" t="n">
         <v>24</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.765</v>
+        <v>0.761</v>
       </c>
       <c r="R30" t="n">
         <v>12.2</v>
@@ -5805,13 +5872,13 @@
         <v>29.8</v>
       </c>
       <c r="T30" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U30" t="n">
         <v>22.8</v>
       </c>
       <c r="V30" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W30" t="n">
         <v>8.300000000000001</v>
@@ -5823,31 +5890,31 @@
         <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA30" t="n">
         <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>12</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI30" t="n">
         <v>17</v>
@@ -5856,7 +5923,7 @@
         <v>20</v>
       </c>
       <c r="AK30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="n">
         <v>23</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5886,7 +5953,7 @@
         <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV30" t="n">
         <v>17</v>
@@ -5901,10 +5968,10 @@
         <v>23</v>
       </c>
       <c r="AZ30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-4.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
         <v>28</v>
@@ -6038,7 +6105,7 @@
         <v>13</v>
       </c>
       <c r="AK31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL31" t="n">
         <v>18</v>
@@ -6071,7 +6138,7 @@
         <v>20</v>
       </c>
       <c r="AV31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-9-2012-13</t>
+          <t>2013-02-09</t>
         </is>
       </c>
     </row>
